--- a/survey_templates/036_grant_writing_workshop_feedback_form--survey_templates.xlsx
+++ b/survey_templates/036_grant_writing_workshop_feedback_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Grant Writing Workshop Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_comments</t>
+          <t>grant_writing_workshop_comments_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Grant Writing Workshop Comments 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_comments</t>
+          <t>grant_writing_workshop_comments_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Grant Writing Workshop Comments 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Would you like to agree to participate in future grant writing workshops?</t>
+          <t>Grant Writing Workshop Agreement</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_agreed</t>
+          <t>grant_writing_workshop_agreed_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Would you like to agree to have the workshop organizers contact you to discuss your feedback?</t>
+          <t>Grant Writing Workshop Agreed 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Would you like to agree to allow workshop organizers to contact you via email?</t>
+          <t>Grant Writing Workshop Email Agreed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Would you like to agree to allow workshop organizers to contact you via phone?</t>
+          <t>Grant Writing Workshop Phone Agreed</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_agreed</t>
+          <t>grant_writing_workshop_agreed_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_agreed_choices</t>
+          <t>grant_writing_workshop_agreed_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_agreed_choices</t>
+          <t>grant_writing_workshop_agreed_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1857,7 +1857,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_agreed_choices</t>
+          <t>grant_writing_workshop_agreed_3_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1874,7 +1874,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>grant_writing_workshop_agreed_choices</t>
+          <t>grant_writing_workshop_agreed_3_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
